--- a/public/assets/excel/shift_plans.xlsx
+++ b/public/assets/excel/shift_plans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo LOQ\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298CCB8B-A7F7-4DDF-A053-CF716D07209A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA0452C-E047-4F55-A1BC-D32773203784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,165 +20,189 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="53">
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Clock_in_time</t>
-  </si>
-  <si>
-    <t>Clock_out_time</t>
-  </si>
-  <si>
-    <t>Treat_as_full_day_minutes</t>
-  </si>
-  <si>
-    <t>Treat_as_half_day_minutes</t>
-  </si>
-  <si>
-    <t>Grace_time</t>
-  </si>
-  <si>
-    <t>Late_after_minutes</t>
-  </si>
-  <si>
-    <t>Excessive_late_after_minutes</t>
-  </si>
-  <si>
-    <t>Early_out_grace_minutes</t>
-  </si>
-  <si>
-    <t>Breakfast_status</t>
-  </si>
-  <si>
-    <t>Breakfast_start_time</t>
-  </si>
-  <si>
-    <t>Breakfast_end_time</t>
-  </si>
-  <si>
-    <t>Lunch_status</t>
-  </si>
-  <si>
-    <t>Lunch_start_time</t>
-  </si>
-  <si>
-    <t>Lunch_end_time</t>
-  </si>
-  <si>
-    <t>Snacks_status</t>
-  </si>
-  <si>
-    <t>Snacks_start_time</t>
-  </si>
-  <si>
-    <t>Snacks_end_time</t>
-  </si>
-  <si>
-    <t>Dinner_status</t>
-  </si>
-  <si>
-    <t>Dinner_start_time</t>
-  </si>
-  <si>
-    <t>Dinner_end_time</t>
-  </si>
-  <si>
-    <t>Active_ind</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
+  <si>
+    <t>clock_in_time</t>
+  </si>
+  <si>
+    <t>clock_out_time</t>
+  </si>
+  <si>
+    <t>treat_as_full_day_minutes</t>
+  </si>
+  <si>
+    <t>treat_as_half_day_minutes</t>
+  </si>
+  <si>
+    <t>grace_time</t>
+  </si>
+  <si>
+    <t>late_after_minutes</t>
+  </si>
+  <si>
+    <t>excessive_late_after_minutes</t>
+  </si>
+  <si>
+    <t>early_out_grace_minutes</t>
+  </si>
+  <si>
+    <t>early_out_before</t>
+  </si>
+  <si>
+    <t>breakfast_status</t>
+  </si>
+  <si>
+    <t>breakfast_start_time</t>
+  </si>
+  <si>
+    <t>breakfast_end_time</t>
+  </si>
+  <si>
+    <t>lunch_status</t>
+  </si>
+  <si>
+    <t>lunch_start_time</t>
+  </si>
+  <si>
+    <t>lunch_end_time</t>
+  </si>
+  <si>
+    <t>snacks_status</t>
+  </si>
+  <si>
+    <t>snacks_start_time</t>
+  </si>
+  <si>
+    <t>snacks_end_time</t>
+  </si>
+  <si>
+    <t>dinner_status</t>
+  </si>
+  <si>
+    <t>dinner_start_time</t>
+  </si>
+  <si>
+    <t>dinner_end_time</t>
+  </si>
+  <si>
+    <t>Morning Shift A</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>20:00</t>
   </si>
   <si>
     <t>09:30</t>
   </si>
   <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>inactive</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>Morning 1</t>
-  </si>
-  <si>
-    <t>Morning 2</t>
-  </si>
-  <si>
-    <t>Morning 3</t>
-  </si>
-  <si>
-    <t>Morning 4</t>
-  </si>
-  <si>
-    <t>Morning 5</t>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>Shift_name</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Morning Shift B</t>
+  </si>
+  <si>
+    <t>Morning Shift C</t>
+  </si>
+  <si>
+    <t>Morning Shift D</t>
+  </si>
+  <si>
+    <t>Morning Shift E</t>
   </si>
 </sst>
 </file>
@@ -260,9 +284,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -300,9 +324,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -335,26 +359,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -387,26 +394,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -580,110 +570,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:W6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>48</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2">
         <v>480</v>
@@ -695,7 +689,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -707,39 +701,42 @@
         <v>31</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>480</v>
@@ -748,60 +745,57 @@
         <v>240</v>
       </c>
       <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3">
         <v>10</v>
       </c>
-      <c r="G3">
-        <v>15</v>
-      </c>
       <c r="H3">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I3">
         <v>5</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P3" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="S3" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" t="s">
-        <v>30</v>
+        <v>49</v>
+      </c>
+      <c r="T3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>480</v>
@@ -810,161 +804,149 @@
         <v>240</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>60</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>37</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" t="s">
+        <v>53</v>
+      </c>
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>240</v>
+      </c>
+      <c r="E5">
+        <v>120</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>15</v>
-      </c>
-      <c r="H4">
-        <v>30</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s">
-        <v>31</v>
-      </c>
-      <c r="T4" t="s">
-        <v>44</v>
-      </c>
-      <c r="U4" t="s">
-        <v>46</v>
-      </c>
-      <c r="V4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5">
-        <v>480</v>
-      </c>
-      <c r="E5">
-        <v>240</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>30</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" t="s">
-        <v>40</v>
-      </c>
-      <c r="P5" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>37</v>
+      </c>
+      <c r="T5" t="s">
+        <v>37</v>
+      </c>
+      <c r="W5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="S5" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U5" t="s">
-        <v>47</v>
-      </c>
-      <c r="V5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
       <c r="D6">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="E6">
-        <v>240</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" t="s">
-        <v>30</v>
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>43</v>
       </c>
       <c r="P6" t="s">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
+        <v>48</v>
       </c>
       <c r="S6" t="s">
-        <v>30</v>
+        <v>50</v>
+      </c>
+      <c r="T6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" t="s">
+        <v>52</v>
       </c>
       <c r="V6" t="s">
-        <v>31</v>
+        <v>54</v>
+      </c>
+      <c r="W6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/excel/shift_plans.xlsx
+++ b/public/assets/excel/shift_plans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA0452C-E047-4F55-A1BC-D32773203784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2911666D-9D79-48F8-BA60-03810BABFD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,189 +20,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
-  <si>
-    <t>clock_in_time</t>
-  </si>
-  <si>
-    <t>clock_out_time</t>
-  </si>
-  <si>
-    <t>treat_as_full_day_minutes</t>
-  </si>
-  <si>
-    <t>treat_as_half_day_minutes</t>
-  </si>
-  <si>
-    <t>grace_time</t>
-  </si>
-  <si>
-    <t>late_after_minutes</t>
-  </si>
-  <si>
-    <t>excessive_late_after_minutes</t>
-  </si>
-  <si>
-    <t>early_out_grace_minutes</t>
-  </si>
-  <si>
-    <t>early_out_before</t>
-  </si>
-  <si>
-    <t>breakfast_status</t>
-  </si>
-  <si>
-    <t>breakfast_start_time</t>
-  </si>
-  <si>
-    <t>breakfast_end_time</t>
-  </si>
-  <si>
-    <t>lunch_status</t>
-  </si>
-  <si>
-    <t>lunch_start_time</t>
-  </si>
-  <si>
-    <t>lunch_end_time</t>
-  </si>
-  <si>
-    <t>snacks_status</t>
-  </si>
-  <si>
-    <t>snacks_start_time</t>
-  </si>
-  <si>
-    <t>snacks_end_time</t>
-  </si>
-  <si>
-    <t>dinner_status</t>
-  </si>
-  <si>
-    <t>dinner_start_time</t>
-  </si>
-  <si>
-    <t>dinner_end_time</t>
-  </si>
-  <si>
-    <t>Morning Shift A</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>12:25</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="42">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Clock_in_time</t>
+  </si>
+  <si>
+    <t>Clock_out_time</t>
+  </si>
+  <si>
+    <t>Treat_as_full_day_minutes</t>
+  </si>
+  <si>
+    <t>Treat_as_half_day_minutes</t>
+  </si>
+  <si>
+    <t>Grace_time</t>
+  </si>
+  <si>
+    <t>Late_after_minutes</t>
+  </si>
+  <si>
+    <t>Excessive_late_after_minutes</t>
+  </si>
+  <si>
+    <t>Early_out_grace_minutes</t>
+  </si>
+  <si>
+    <t>Breakfast_status</t>
+  </si>
+  <si>
+    <t>Breakfast_start_time</t>
+  </si>
+  <si>
+    <t>Breakfast_end_time</t>
+  </si>
+  <si>
+    <t>Lunch_status</t>
+  </si>
+  <si>
+    <t>Lunch_start_time</t>
+  </si>
+  <si>
+    <t>Lunch_end_time</t>
+  </si>
+  <si>
+    <t>Snacks_status</t>
+  </si>
+  <si>
+    <t>Snacks_start_time</t>
+  </si>
+  <si>
+    <t>Snacks_end_time</t>
+  </si>
+  <si>
+    <t>Dinner_status</t>
+  </si>
+  <si>
+    <t>Dinner_start_time</t>
+  </si>
+  <si>
+    <t>Dinner_end_time</t>
+  </si>
+  <si>
+    <t>inactive</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
-    <t>inactive</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>Shift_name</t>
+    <t>Morning 1</t>
+  </si>
+  <si>
+    <t>Morning 2</t>
+  </si>
+  <si>
+    <t>Morning 3</t>
+  </si>
+  <si>
+    <t>Morning 4</t>
+  </si>
+  <si>
+    <t>Morning 5</t>
+  </si>
+  <si>
+    <t>9.30 AM</t>
+  </si>
+  <si>
+    <t>10.30 AM</t>
+  </si>
+  <si>
+    <t>8.30 AM</t>
+  </si>
+  <si>
+    <t>7.30 AM</t>
+  </si>
+  <si>
+    <t>6.00 PM</t>
+  </si>
+  <si>
+    <t>10.15 AM</t>
+  </si>
+  <si>
+    <t>11.00 AM</t>
+  </si>
+  <si>
+    <t>1.15 PM</t>
+  </si>
+  <si>
+    <t>1.45 PM</t>
+  </si>
+  <si>
+    <t>4.15 PM</t>
+  </si>
+  <si>
+    <t>4.30 PM</t>
+  </si>
+  <si>
+    <t>8.15 PM</t>
+  </si>
+  <si>
+    <t>8.45 PM</t>
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Morning Shift B</t>
-  </si>
-  <si>
-    <t>Morning Shift C</t>
-  </si>
-  <si>
-    <t>Morning Shift D</t>
-  </si>
-  <si>
-    <t>Morning Shift E</t>
   </si>
 </sst>
 </file>
@@ -261,11 +204,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,114 +517,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="D2">
         <v>480</v>
@@ -689,7 +632,7 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -698,45 +641,42 @@
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="P2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
+      <c r="C3" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="D3">
         <v>480</v>
@@ -745,57 +685,60 @@
         <v>240</v>
       </c>
       <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>15</v>
       </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
       <c r="H3">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I3">
         <v>5</v>
       </c>
       <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>21</v>
+      </c>
+      <c r="V3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" t="s">
-        <v>47</v>
-      </c>
-      <c r="S3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T3" t="s">
-        <v>37</v>
-      </c>
-      <c r="W3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
       </c>
       <c r="D4">
         <v>480</v>
@@ -804,149 +747,161 @@
         <v>240</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U4" t="s">
+        <v>40</v>
+      </c>
+      <c r="V4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>480</v>
+      </c>
+      <c r="E5">
+        <v>240</v>
+      </c>
+      <c r="F5">
         <v>10</v>
       </c>
-      <c r="J4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" t="s">
-        <v>51</v>
-      </c>
-      <c r="V4" t="s">
-        <v>53</v>
-      </c>
-      <c r="W4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5">
-        <v>240</v>
-      </c>
-      <c r="E5">
-        <v>120</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
       <c r="G5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H5">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+      <c r="T5" t="s">
         <v>39</v>
       </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>37</v>
-      </c>
-      <c r="T5" t="s">
-        <v>37</v>
-      </c>
-      <c r="W5" t="s">
-        <v>37</v>
+      <c r="U5" t="s">
+        <v>40</v>
+      </c>
+      <c r="V5" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <v>480</v>
+      </c>
+      <c r="E6">
+        <v>240</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
         <v>30</v>
-      </c>
-      <c r="D6">
-        <v>300</v>
-      </c>
-      <c r="E6">
-        <v>150</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" t="s">
-        <v>43</v>
+        <v>22</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="S6" t="s">
-        <v>50</v>
-      </c>
-      <c r="T6" t="s">
-        <v>36</v>
-      </c>
-      <c r="U6" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="V6" t="s">
-        <v>54</v>
-      </c>
-      <c r="W6" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
